--- a/HRMS.Web/HRMS.Web/wwwroot/assets/DownloadExcel/AttendanceImport.xlsx
+++ b/HRMS.Web/HRMS.Web/wwwroot/assets/DownloadExcel/AttendanceImport.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\14119\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My-PC-Download-Backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0969A5A5-E5C3-4D0B-881C-ADB63D98BBB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD126CB-B70D-4832-84EC-B90E0248013A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{1429A4FB-6599-4AC0-813C-D572397353AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Attendance!$A$1:$AG$3</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -37,7 +37,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="7">
+  <si>
+    <t>EmployeeName</t>
+  </si>
   <si>
     <t>P</t>
   </si>
@@ -45,66 +48,58 @@
     <t>WO</t>
   </si>
   <si>
-    <t>Device issue</t>
+    <t>H</t>
   </si>
   <si>
-    <t>Missed punch</t>
+    <t>Gaurav Vohra</t>
   </si>
   <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Manjeet Kumar</t>
-  </si>
-  <si>
-    <t>Jyoti</t>
+    <t>Reshma</t>
   </si>
   <si>
     <t>EmployeeNumber</t>
-  </si>
-  <si>
-    <t>EmployeeName</t>
-  </si>
-  <si>
-    <t>WorkDate</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Remarks</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mmm/yy\ ddd"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Candara"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Candara"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -112,20 +107,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,200 +462,351 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CC07899-5E02-47BE-98FA-D98BCC2DFD1B}">
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AG3"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" style="6" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="5" customWidth="1"/>
+    <col min="16" max="16" width="12.140625" style="5" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" style="5" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="11.42578125" style="5" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" style="5" customWidth="1"/>
+    <col min="21" max="21" width="11" style="5" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="11.85546875" style="5" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="5" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" style="5" customWidth="1"/>
+    <col min="26" max="26" width="11.140625" style="5" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" style="5" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" style="5" customWidth="1"/>
+    <col min="29" max="29" width="11.140625" style="5" customWidth="1"/>
+    <col min="30" max="30" width="11.85546875" style="5" customWidth="1"/>
+    <col min="31" max="31" width="11" style="5" customWidth="1"/>
+    <col min="32" max="32" width="11.85546875" style="5" customWidth="1"/>
+    <col min="33" max="33" width="11.42578125" style="5" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="C1" s="7">
+        <v>46224</v>
+      </c>
+      <c r="D1" s="7">
+        <v>46225</v>
+      </c>
+      <c r="E1" s="7">
+        <v>46226</v>
+      </c>
+      <c r="F1" s="7">
+        <v>46227</v>
+      </c>
+      <c r="G1" s="7">
+        <v>46228</v>
+      </c>
+      <c r="H1" s="7">
+        <v>46229</v>
+      </c>
+      <c r="I1" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J1" s="7">
+        <v>46231</v>
+      </c>
+      <c r="K1" s="7">
+        <v>46232</v>
+      </c>
+      <c r="L1" s="7">
+        <v>46233</v>
+      </c>
+      <c r="M1" s="7">
+        <v>46234</v>
+      </c>
+      <c r="N1" s="7">
+        <v>46235</v>
+      </c>
+      <c r="O1" s="7">
+        <v>46236</v>
+      </c>
+      <c r="P1" s="7">
+        <v>46237</v>
+      </c>
+      <c r="Q1" s="7">
+        <v>46238</v>
+      </c>
+      <c r="R1" s="7">
+        <v>46239</v>
+      </c>
+      <c r="S1" s="7">
+        <v>46240</v>
+      </c>
+      <c r="T1" s="7">
+        <v>46241</v>
+      </c>
+      <c r="U1" s="7">
+        <v>46242</v>
+      </c>
+      <c r="V1" s="7">
+        <v>46243</v>
+      </c>
+      <c r="W1" s="7">
+        <v>46244</v>
+      </c>
+      <c r="X1" s="7">
+        <v>46245</v>
+      </c>
+      <c r="Y1" s="7">
+        <v>46246</v>
+      </c>
+      <c r="Z1" s="7">
+        <v>46247</v>
+      </c>
+      <c r="AA1" s="7">
+        <v>46248</v>
+      </c>
+      <c r="AB1" s="7">
+        <v>46249</v>
+      </c>
+      <c r="AC1" s="7">
+        <v>46250</v>
+      </c>
+      <c r="AD1" s="7">
+        <v>46251</v>
+      </c>
+      <c r="AE1" s="7">
+        <v>46252</v>
+      </c>
+      <c r="AF1" s="7">
+        <v>46253</v>
+      </c>
+      <c r="AG1" s="7">
+        <v>46254</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>10061</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>10004</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>10020</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3">
-        <v>46224</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>10061</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46232</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>10096</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46225</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>10096</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3">
-        <v>46226</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>10096</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46232</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>10096</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46194</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2"/>
+      <c r="AC3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>